--- a/panele-sterowania/Panel-A.xlsx
+++ b/panele-sterowania/Panel-A.xlsx
@@ -10,14 +10,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ulepszenia-FOOD" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ulepszenia-inne" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plony-terenow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruch-po-terenie" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zasięgi-mgła" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-rozmiary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zloza-generator" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-E2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa-skala" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Eksporty" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruch-po-terenie" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zasięgi-mgła" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-rozmiary" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zloza-generator" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-E2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa-skala" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Eksporty" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teren-bazowy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bonusy-nakladki" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -48,8 +49,20 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF1F4E79"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +72,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -84,6 +102,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -462,19 +486,14 @@
           <t>Panel sterowania — GRUPA A (Mapa / ulepszenia / generator)</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-    </row>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Jak używać (Maciej)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -512,10 +531,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -606,392 +622,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Parametr</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Opis</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Wartość</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Zakres/dozwolone</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Jednostka</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Wpływ na grę</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Plik źródłowy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-MAL</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.mala</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Mała</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-MAL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.mala</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Mała</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-SRE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.srednia</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Średnia</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-SRE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.srednia</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Średnia</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-DUZ</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.duza</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Duża</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-DUZ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.duza</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Duża</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-OGR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.ogromna</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Ogromna</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-OGR</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.ogromna</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Ogromna</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1044,6 +674,289 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>terrain-improvements · terrain-yields · terrain-movement · map-gen-params</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Edycja → w czacie: eksportuj plony terenu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Teren</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Żywność</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Praca</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Handel</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Łąka</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Równina</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Wzgórza</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Kamień/Ruda po zbudowaniu Kopalni; +obrona</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Góry</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Nieprzechodnie dla jednostek lądowych; Kamień/Ruda po Kopalni</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Wybrzeże</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Teren morski przy lądzie (osobny od rzeki); pod port</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Morze</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Otwarta woda; rybołówstwo</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Pustynia</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Edycja → w czacie: eksportuj plony terenu</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Modyfikator</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Żywność</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Praca</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Handel</t>
+        </is>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Uwagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Rzeka</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Dodaje bonus do DOWOLNEGO pola z rzeką (Twój opis); razem +7 — mocny, można stonować</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Las (nakładka)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Pod lasem zawsze jest teren bazowy; las: −żywność, −handel, +praca (+3), +drewno — bez względu na 👤/jednostkę</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2431,6 @@
       <c r="D2" t="n">
         <v>25</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -2554,7 +2466,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -2592,7 +2503,6 @@
           <t>ruda</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -2628,7 +2538,6 @@
       <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -2664,7 +2573,6 @@
       <c r="D6" t="n">
         <v>20</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -2700,7 +2608,6 @@
       <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -2738,7 +2645,6 @@
           <t>glina</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -2774,7 +2680,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -2810,7 +2715,6 @@
       <c r="D10" t="n">
         <v>22</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -2846,7 +2750,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -2884,7 +2787,6 @@
           <t>kamien</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -2920,7 +2822,6 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -2956,7 +2857,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -2992,7 +2892,6 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3028,7 +2927,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -3061,7 +2959,6 @@
           <t>Wyrąb — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -3097,7 +2994,6 @@
       <c r="D18" t="n">
         <v>20</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3133,7 +3029,6 @@
       <c r="D19" t="n">
         <v>3</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>tury</t>
@@ -3169,7 +3064,6 @@
       <c r="D20" t="n">
         <v>25</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3205,7 +3099,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -3243,7 +3136,6 @@
           <t>drewno</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -3279,7 +3171,6 @@
       <c r="D23" t="n">
         <v>3</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -3315,7 +3206,6 @@
       <c r="D24" t="n">
         <v>25</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3351,7 +3241,6 @@
       <c r="D25" t="n">
         <v>3</v>
       </c>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -3384,7 +3273,6 @@
           <t>Fort / umocnienia — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -3420,7 +3308,6 @@
       <c r="D27" t="n">
         <v>100</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
           <t>%</t>
@@ -3456,7 +3343,6 @@
       <c r="D28" t="b">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
           <t>tak/nie</t>
@@ -3492,7 +3378,6 @@
       <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -3528,7 +3413,6 @@
       <c r="D30" t="n">
         <v>10</v>
       </c>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -3564,7 +3448,6 @@
       <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -3600,7 +3483,6 @@
       <c r="D32" t="n">
         <v>15</v>
       </c>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3636,7 +3518,6 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -3669,7 +3550,6 @@
           <t>Droga — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -3705,7 +3585,6 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -3741,7 +3620,6 @@
       <c r="D36" t="n">
         <v>30</v>
       </c>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3777,7 +3655,6 @@
       <c r="D37" t="n">
         <v>2</v>
       </c>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -3810,7 +3687,6 @@
           <t>Posterunek (Strażnica) — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -3846,7 +3722,6 @@
       <c r="D39" t="n">
         <v>50</v>
       </c>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
           <t>%</t>
@@ -3882,7 +3757,6 @@
       <c r="D40" t="b">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
           <t>tak/nie</t>
@@ -3918,7 +3792,6 @@
       <c r="D41" t="n">
         <v>5</v>
       </c>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -3954,7 +3827,6 @@
       <c r="D42" t="n">
         <v>5</v>
       </c>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -3982,7 +3854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4040,57 +3912,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-PLON-001</t>
+          <t>A-RUCH-LAK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>plony.types.laka.zywnosc</t>
+          <t>ruch.costs.Laka</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Łąka — bazowy plon zywnosc</t>
+          <t>Koszt ruchu jednostki — Łąka</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-PLON-002</t>
+          <t>A-RUCH-ROW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>plony.types.laka.praca</t>
+          <t>ruch.costs.Rownina</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Łąka — bazowy plon praca</t>
+          <t>Koszt ruchu jednostki — Równina</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -4098,239 +3970,239 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-PLON-003</t>
+          <t>A-RUCH-PUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>plony.types.laka.handel</t>
+          <t>ruch.costs.Pustynia</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Łąka — bazowy plon handel</t>
+          <t>Koszt ruchu jednostki — Pustynia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-PLON-004</t>
+          <t>A-RUCH-WYB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>plony.types.laka.drewno</t>
+          <t>ruch.costs.Wybrzeze</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Łąka — bazowy plon drewno</t>
+          <t>Koszt ruchu jednostki — Wybrzeże</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-PLON-005</t>
+          <t>A-RUCH-WZG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>plony.types.laka.kamien</t>
+          <t>ruch.costs.Wzgorza</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Łąka — bazowy plon kamien</t>
+          <t>Koszt ruchu jednostki — Wzgórza</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-PLON-006</t>
+          <t>A-RUCH-GOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>plony.types.rownina.zywnosc</t>
+          <t>ruch.costs.Gory</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Równina — bazowy plon zywnosc</t>
+          <t>Koszt ruchu jednostki — Góry</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>99</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-PLON-007</t>
+          <t>A-RUCH-MOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>plony.types.rownina.praca</t>
+          <t>ruch.costs.Morze</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Równina — bazowy plon praca</t>
+          <t>Koszt ruchu jednostki — Morze</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-PLON-008</t>
+          <t>A-RUCH-LAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>plony.types.rownina.handel</t>
+          <t>ruch.forestExtra</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Równina — bazowy plon handel</t>
+          <t>Dopłata ruchu przez las (nakładka)</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4338,1502 +4210,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0–8 typowo</t>
+          <t>0–3</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>economy.ts tileYield · okolica miasta</t>
+          <t>ruch po heksie z lasem</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A-PLON-009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>plony.types.rownina.drewno</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Równina — bazowy plon drewno</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A-PLON-010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>plony.types.rownina.kamien</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Równina — bazowy plon kamien</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A-PLON-011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>plony.types.wzgorza.zywnosc</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Wzgórza — bazowy plon zywnosc</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A-PLON-012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>plony.types.wzgorza.praca</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Wzgórza — bazowy plon praca</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>A-PLON-013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>plony.types.wzgorza.handel</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Wzgórza — bazowy plon handel</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>A-PLON-014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>plony.types.wzgorza.drewno</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Wzgórza — bazowy plon drewno</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>A-PLON-015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>plony.types.wzgorza.kamien</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Wzgórza — bazowy plon kamien</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>A-PLON-016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>plony.types.gory.zywnosc</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Góry — bazowy plon zywnosc</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>A-PLON-017</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>plony.types.gory.praca</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Góry — bazowy plon praca</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>A-PLON-018</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>plony.types.gory.handel</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Góry — bazowy plon handel</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A-PLON-019</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>plony.types.gory.drewno</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Góry — bazowy plon drewno</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>2</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>A-PLON-020</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>plony.types.gory.kamien</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Góry — bazowy plon kamien</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A-PLON-021</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>plony.types.wybrzeze.zywnosc</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Wybrzeże — bazowy plon zywnosc</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>A-PLON-022</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>plony.types.wybrzeze.praca</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Wybrzeże — bazowy plon praca</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>A-PLON-023</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>plony.types.wybrzeze.handel</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Wybrzeże — bazowy plon handel</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>A-PLON-024</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>plony.types.wybrzeze.drewno</t>
-        </is>
-      </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Wybrzeże — bazowy plon drewno</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>A-PLON-025</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>plony.types.wybrzeze.kamien</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Wybrzeże — bazowy plon kamien</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>A-PLON-026</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>plony.types.morze.zywnosc</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Morze — bazowy plon zywnosc</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>2</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>A-PLON-027</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>plony.types.morze.praca</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Morze — bazowy plon praca</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>A-PLON-028</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>plony.types.morze.handel</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Morze — bazowy plon handel</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>2</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>A-PLON-029</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>plony.types.morze.drewno</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Morze — bazowy plon drewno</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G30" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>A-PLON-030</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>plony.types.morze.kamien</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Morze — bazowy plon kamien</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>A-PLON-031</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>plony.types.pustynia.zywnosc</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Pustynia — bazowy plon zywnosc</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>A-PLON-032</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>plony.types.pustynia.praca</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Pustynia — bazowy plon praca</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>A-PLON-033</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>plony.types.pustynia.handel</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Pustynia — bazowy plon handel</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>A-PLON-034</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>plony.types.pustynia.drewno</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Pustynia — bazowy plon drewno</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>A-PLON-035</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>plony.types.pustynia.kamien</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Pustynia — bazowy plon kamien</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>0–8 typowo</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>economy.ts tileYield · okolica miasta</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>A-PLON-036</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>plony.mod.rzeka.zywnosc</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Rzeka — zywnosc</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>3</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G37" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>A-PLON-037</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>plony.mod.rzeka.praca</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Rzeka — praca</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>A-PLON-038</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>plony.mod.rzeka.handel</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Rzeka — handel</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>2</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>A-PLON-039</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>plony.mod.rzeka.drewno</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Rzeka — drewno</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>A-PLON-040</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>plony.mod.rzeka.kamien</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Rzeka — kamien</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G41" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>A-PLON-041</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>plony.mod.las.zywnosc</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Las (nakładka) — zywnosc</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>A-PLON-042</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>plony.mod.las.praca</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Las (nakładka) — praca</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>A-PLON-043</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>plony.mod.las.handel</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Las (nakładka) — handel</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A-PLON-044</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>plony.mod.las.drewno</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Las (nakładka) — drewno</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>3</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G45" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A-PLON-045</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>plony.mod.las.kamien</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Modyfikator Las (nakładka) — kamien</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-3…+5</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>pkt/turę</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>bonus nakładki / rzeki na heks</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>terrain-yields.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
@@ -5906,320 +4298,290 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-RUCH-LAK</t>
+          <t>A-FOG-SIGHT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ruch.costs.Laka</t>
+          <t>mgla.default_sight_jednostki</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Łąka</t>
+          <t>Domyślny promień wzroku jednostki (hexDistance)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>2–5 typowo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>mgła — visibility.ts DEFAULT_SIGHT (wpięcie Integrator)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-RUCH-ROW</t>
+          <t>A-ZAS-MIASTO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ruch.costs.Rownina</t>
+          <t>nota.miasto_zasieg_terytorium</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Równina</t>
+          <t>NOTA: miasto bazowe zasięg terytorium (nie ulepszenie)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>stałe ref EKONOMIA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>zakładanie kolejnego miasta — Panel-B / cities</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>(tylko nota — bez eksportu)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-RUCH-PUS</t>
+          <t>A-ZAS-POST-ZAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ruch.costs.Pustynia</t>
+          <t>posterunek.zasieg_terytorium</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Pustynia</t>
+          <t>Posterunek — zasieg terytorium</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1–99 (99=nieprzechodnie)</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-RUCH-WYB</t>
+          <t>A-ZAS-POST-ZAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ruch.costs.Wybrzeze</t>
+          <t>posterunek.zasieg_pol</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Wybrzeże</t>
+          <t>Posterunek — zasieg pol</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>99</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1–99 (99=nieprzechodnie)</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-RUCH-WZG</t>
+          <t>A-ZAS-POST-BON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ruch.costs.Wzgorza</t>
+          <t>posterunek.bonus_obrona_proc</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Wzgórza</t>
+          <t>Posterunek — bonus obrona proc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>1–99 (99=nieprzechodnie)</t>
-        </is>
+        <v>50</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-RUCH-GOR</t>
+          <t>A-ZAS-FORT-ZAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ruch.costs.Gory</t>
+          <t>fort.zasieg_terytorium</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Góry</t>
+          <t>Fort — zasieg terytorium</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1–99 (99=nieprzechodnie)</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-RUCH-MOR</t>
+          <t>A-ZAS-FORT-ZAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ruch.costs.Morze</t>
+          <t>fort.zasieg_pol</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Morze</t>
+          <t>Fort — zasieg pol</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1–99 (99=nieprzechodnie)</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-RUCH-LAS</t>
+          <t>A-ZAS-FORT-BON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ruch.forestExtra</t>
+          <t>fort.bonus_obrona_proc</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Dopłata ruchu przez las (nakładka)</t>
+          <t>Fort — bonus obrona proc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0–3</t>
-        </is>
+        <v>100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>ruch po heksie z lasem</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
@@ -6234,7 +4596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6292,25 +4654,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-FOG-SIGHT</t>
+          <t>A-GEN-DEF-W</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mgla.default_sight_jednostki</t>
+          <t>generator.default_width</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Domyślny promień wzroku jednostki (hexDistance)</t>
+          <t>Domyślna szerokość siatki (dev / fallback generator.ts)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2–5 typowo</t>
+          <t>20–200</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -6320,37 +4682,37 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>mgła — visibility.ts DEFAULT_SIGHT (wpięcie Integrator)</t>
+          <t>generateMap() gdy brak rozmiaru z menu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>map-gen-params.json (wpięcie Integrator P3)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-ZAS-MIASTO</t>
+          <t>A-GEN-DEF-H</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nota.miasto_zasieg_terytorium</t>
+          <t>generator.default_height</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>NOTA: miasto bazowe zasięg terytorium (nie ulepszenie)</t>
+          <t>Domyślna wysokość siatki (dev / fallback)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stałe ref EKONOMIA</t>
+          <t>15–150</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -6360,35 +4722,34 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>zakładanie kolejnego miasta — Panel-B / cities</t>
+          <t>generateMap() fallback</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(tylko nota — bez eksportu)</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-ZAS-POST-ZAS</t>
+          <t>A-GEN-MAL-W</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>posterunek.zasieg_terytorium</t>
+          <t>generator.rozmiar_dims.malenki.w</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Posterunek — zasieg terytorium</t>
+          <t>Rozmiar mapy Malenki — szerokość</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>38</v>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -6396,35 +4757,34 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-ZAS-POST-ZAS</t>
+          <t>A-GEN-MAL-H</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>posterunek.zasieg_pol</t>
+          <t>generator.rozmiar_dims.malenki.h</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Posterunek — zasieg pol</t>
+          <t>Rozmiar mapy Malenki — wysokość</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>26</v>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -6432,71 +4792,69 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-ZAS-POST-BON</t>
+          <t>A-GEN-MAL-W</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>posterunek.bonus_obrona_proc</t>
+          <t>generator.rozmiar_dims.maly.w</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Posterunek — bonus obrona proc</t>
+          <t>Rozmiar mapy Mały — szerokość</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>54</v>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-ZAS-FORT-ZAS</t>
+          <t>A-GEN-MAL-H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fort.zasieg_terytorium</t>
+          <t>generator.rozmiar_dims.maly.h</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Fort — zasieg terytorium</t>
+          <t>Rozmiar mapy Mały — wysokość</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>37</v>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -6504,35 +4862,34 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-ZAS-FORT-ZAS</t>
+          <t>A-GEN-STA-W</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fort.zasieg_pol</t>
+          <t>generator.rozmiar_dims.standardowy.w</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Fort — zasieg pol</t>
+          <t>Rozmiar mapy Standardowy — szerokość</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>84</v>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -6540,48 +4897,187 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-ZAS-FORT-BON</t>
+          <t>A-GEN-STA-H</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fort.bonus_obrona_proc</t>
+          <t>generator.rozmiar_dims.standardowy.h</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Fort — bonus obrona proc</t>
+          <t>Rozmiar mapy Standardowy — wysokość</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>60</v>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A-GEN-DUZ-W</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>generator.rozmiar_dims.duzy.w</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Rozmiar mapy Duży — szerokość</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>120</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>heksy</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>menuLabelToDims · generujSwiat</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A-GEN-DUZ-H</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>generator.rozmiar_dims.duzy.h</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Rozmiar mapy Duży — wysokość</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>84</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>heksy</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>menuLabelToDims · generujSwiat</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A-GEN-OGR-W</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>generator.rozmiar_dims.ogromny.w</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Rozmiar mapy Ogromny — szerokość</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>168</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>heksy</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>menuLabelToDims · generujSwiat</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A-GEN-OGR-H</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>generator.rozmiar_dims.ogromny.h</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Rozmiar mapy Ogromny — wysokość</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>119</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>heksy</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>menuLabelToDims · generujSwiat</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
@@ -6654,75 +5150,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-GEN-DEF-W</t>
+          <t>A-ZLO-R-MIED</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>generator.default_width</t>
+          <t>zloza.miedz.rarity</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Domyślna szerokość siatki (dev / fallback generator.ts)</t>
+          <t>Rzadkość złoża „miedz” (placeDeposits)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>0.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20–200</t>
+          <t>0,02–0,25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>generateMap() gdy brak rozmiaru z menu</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>map-gen-params.json (wpięcie Integrator P3)</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-GEN-DEF-H</t>
+          <t>A-ZLO-R-ZELA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>generator.default_height</t>
+          <t>zloza.zelazo.rarity</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Domyślna wysokość siatki (dev / fallback)</t>
+          <t>Rzadkość złoża „zelazo” (placeDeposits)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>0.08</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15–150</t>
+          <t>0,02–0,25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>generateMap() fallback</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6734,31 +5230,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-W</t>
+          <t>A-ZLO-R-GLIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.malenki.w</t>
+          <t>zloza.glina.rarity</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Malenki — szerokość</t>
+          <t>Rzadkość złoża „glina” (placeDeposits)</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6770,31 +5270,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-H</t>
+          <t>A-ZLO-R-KONI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.malenki.h</t>
+          <t>zloza.konie.rarity</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Malenki — wysokość</t>
+          <t>Rzadkość złoża „konie” (placeDeposits)</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6806,31 +5310,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-W</t>
+          <t>A-ZLO-R-WEGI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.maly.w</t>
+          <t>zloza.wegiel.rarity</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Mały — szerokość</t>
+          <t>Rzadkość złoża „wegiel” (placeDeposits)</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>0.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6842,31 +5350,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-H</t>
+          <t>A-ZLO-R-OWCE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.maly.h</t>
+          <t>zloza.owce.rarity</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Mały — wysokość</t>
+          <t>Rzadkość złoża „owce” (placeDeposits)</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>0.08</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -6878,31 +5390,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-GEN-STA-W</t>
+          <t>A-ZLO-R-BYDL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.standardowy.w</t>
+          <t>zloza.bydlo.rarity</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Standardowy — szerokość</t>
+          <t>Rzadkość złoża „bydlo” (placeDeposits)</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -6914,31 +5430,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-GEN-STA-H</t>
+          <t>A-ZLO-R-LAMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.standardowy.h</t>
+          <t>zloza.lama.rarity</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Standardowy — wysokość</t>
+          <t>Rzadkość złoża „lama” (placeDeposits)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>0.06</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -6950,31 +5470,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A-GEN-DUZ-W</t>
+          <t>A-ZLO-R-LUKS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.duzy.w</t>
+          <t>zloza.luksus.rarity</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Duży — szerokość</t>
+          <t>Rzadkość złoża „luksus” (placeDeposits)</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>120</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+        <v>0.06</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -6986,31 +5510,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-GEN-DUZ-H</t>
+          <t>A-ZLO-R-SOL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.duzy.h</t>
+          <t>zloza.sol.rarity</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Duży — wysokość</t>
+          <t>Rzadkość złoża „sol” (placeDeposits)</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>84</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>0.12</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>0–1 ułamek</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -7022,31 +5550,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-GEN-OGR-W</t>
+          <t>A-ZLO-E-MIED</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.ogromny.w</t>
+          <t>zloza.miedz.min_epoka</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Ogromny — szerokość</t>
+          <t>Minimalna epoka widoczności złoża „miedz”</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>168</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>1=Kamień…3=Żelazo</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>deposit-era.ts · mgła surowców</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -7058,31 +5590,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A-GEN-OGR-H</t>
+          <t>A-ZLO-E-ZELA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.ogromny.h</t>
+          <t>zloza.zelazo.min_epoka</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Ogromny — wysokość</t>
+          <t>Minimalna epoka widoczności złoża „zelazo”</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>1=Kamień…3=Żelazo</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>deposit-era.ts · mgła surowców</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -7097,552 +5633,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Parametr</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Opis</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Wartość</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Zakres/dozwolone</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Jednostka</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Wpływ na grę</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Plik źródłowy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-MIED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>zloza.miedz.rarity</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „miedz” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-ZELA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>zloza.zelazo.rarity</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „zelazo” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-GLIN</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>zloza.glina.rarity</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „glina” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-KONI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>zloza.konie.rarity</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „konie” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-WEGI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>zloza.wegiel.rarity</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „wegiel” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-OWCE</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>zloza.owce.rarity</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „owce” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-BYDL</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>zloza.bydlo.rarity</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „bydlo” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-LAMA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>zloza.lama.rarity</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „lama” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-LUKS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>zloza.luksus.rarity</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „luksus” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A-ZLO-R-SOL</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>zloza.sol.rarity</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Rzadkość złoża „sol” (placeDeposits)</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0–1 ułamek</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A-ZLO-E-MIED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>zloza.miedz.min_epoka</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Minimalna epoka widoczności złoża „miedz”</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>1=Kamień…3=Żelazo</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>deposit-era.ts · mgła surowców</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A-ZLO-E-ZELA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>zloza.zelazo.min_epoka</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Minimalna epoka widoczności złoża „zelazo”</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1=Kamień…3=Żelazo</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>deposit-era.ts · mgła surowców</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8042,7 +6032,6 @@
       <c r="D10" t="n">
         <v>0.63</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -8078,7 +6067,6 @@
       <c r="D11" t="n">
         <v>0.58</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -8114,7 +6102,6 @@
       <c r="D12" t="n">
         <v>0.65</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -8150,7 +6137,6 @@
       <c r="D13" t="n">
         <v>0.58</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -8186,7 +6172,6 @@
       <c r="D14" t="n">
         <v>0.5</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -8360,6 +6345,392 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>map-gen-params.json (kod P3)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Zakres/dozwolone</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Wpływ na grę</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Plik źródłowy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-MAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.mala</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Mała</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-MAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.mala</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Mała</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-SRE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.srednia</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Średnia</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-SRE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.srednia</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Średnia</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-DUZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.duza</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Duża</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-DUZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.duza</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Duża</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-OGR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.ogromna</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Ogromna</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-OGR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.ogromna</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Ogromna</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>

--- a/panele-sterowania/Panel-A.xlsx
+++ b/panele-sterowania/Panel-A.xlsx
@@ -10,15 +10,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ulepszenia-FOOD" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ulepszenia-inne" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruch-po-terenie" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zasięgi-mgła" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-rozmiary" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zloza-generator" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-E2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa-skala" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Eksporty" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teren-bazowy" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bonusy-nakladki" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plony-terenow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruch-po-terenie" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zasięgi-mgła" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-rozmiary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zloza-generator" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-E2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa-skala" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Eksporty" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,20 +48,8 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF1F4E79"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -72,11 +59,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -92,7 +74,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,12 +84,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -486,14 +462,19 @@
           <t>Panel sterowania — GRUPA A (Mapa / ulepszenia / generator)</t>
         </is>
       </c>
-    </row>
-    <row r="2"/>
+      <c r="B1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>Jak używać (Maciej)</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -531,7 +512,10 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+    </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -612,7 +596,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gen-panel-a.py · 2026-07-01</t>
+          <t>gen-panel-a.py · 2026-07-09</t>
         </is>
       </c>
     </row>
@@ -622,6 +606,392 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Zakres/dozwolone</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Wpływ na grę</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Plik źródłowy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-MAL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.mala</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Mała</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-MAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.mala</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Mała</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-SRE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.srednia</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Średnia</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-SRE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.srednia</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Średnia</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-DUZ</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.duza</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Duża</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-DUZ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.duza</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Duża</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A-MAP-TYP-OGR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>mapa_skala.aktywne_typy.ogromna</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Aktywne typy cywilizacji na mapie Ogromna</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>3–9</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>typy</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>cluster spawn · E2-Q1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A-MAP-RYW-OGR</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mapa_skala.domyslni_rywale.ogromna</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Domyślna liczba rywali AI — mapa Ogromna</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1–8</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>cyw</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>kreator nowej gry</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -674,289 +1044,6 @@
       <c r="B5" t="inlineStr">
         <is>
           <t>terrain-improvements · terrain-yields · terrain-movement · map-gen-params</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Edycja → w czacie: eksportuj plony terenu</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Teren</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Żywność</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Praca</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Handel</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Uwagi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Łąka</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Równina</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Wzgórza</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Kamień/Ruda po zbudowaniu Kopalni; +obrona</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Góry</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Nieprzechodnie dla jednostek lądowych; Kamień/Ruda po Kopalni</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Wybrzeże</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>Teren morski przy lądzie (osobny od rzeki); pod port</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morze</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Otwarta woda; rybołówstwo</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Pustynia</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Edycja → w czacie: eksportuj plony terenu</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Modyfikator</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>Żywność</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Praca</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="inlineStr">
-        <is>
-          <t>Handel</t>
-        </is>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Uwagi</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Rzeka</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Dodaje bonus do DOWOLNEGO pola z rzeką (Twój opis); razem +7 — mocny, można stonować</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Las (nakładka)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Pod lasem zawsze jest teren bazowy; las: −żywność, −handel, +praca (+3), +drewno — bez względu na 👤/jednostkę</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H42"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2420,17 +2507,18 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>kopalnia.koszt_praca</t>
+          <t>stadnina.koszt_praca</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Kopalnia — Koszt budowy</t>
+          <t>Stadnina — Koszt budowy</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -2438,7 +2526,7 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie kopalnia · placement/render MAPA</t>
+          <t>ulepszenie stadnina · placement/render MAPA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2455,17 +2543,18 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>kopalnia.epoka</t>
+          <t>stadnina.epoka</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Kopalnia — Epoka odblokowania</t>
+          <t>Stadnina — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -2473,7 +2562,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie kopalnia · placement/render MAPA</t>
+          <t>ulepszenie stadnina · placement/render MAPA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2490,19 +2579,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kopalnia.surowiecOdblokowany</t>
+          <t>stadnina.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Kopalnia — Odblokowany surowiec (ASCII)</t>
+          <t>Stadnina — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ruda</t>
-        </is>
-      </c>
+          <t>kon</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -2510,7 +2600,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie kopalnia · placement/render MAPA</t>
+          <t>ulepszenie stadnina · placement/render MAPA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2527,17 +2617,18 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>kopalnia.bonus.praca</t>
+          <t>stadnina.bonus.praca</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Kopalnia — bonus praca</t>
+          <t>Stadnina — bonus praca</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -2562,17 +2653,18 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>glinianka.koszt_praca</t>
+          <t>kopalnia.koszt_praca</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Glinianka — Koszt budowy</t>
+          <t>Kopalnia — Koszt budowy</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -2580,7 +2672,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie glinianka · placement/render MAPA</t>
+          <t>ulepszenie kopalnia · placement/render MAPA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2597,17 +2689,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>glinianka.epoka</t>
+          <t>kopalnia.epoka</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Glinianka — Epoka odblokowania</t>
+          <t>Kopalnia — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -2615,7 +2708,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie glinianka · placement/render MAPA</t>
+          <t>ulepszenie kopalnia · placement/render MAPA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2632,19 +2725,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>glinianka.surowiecOdblokowany</t>
+          <t>kopalnia.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Glinianka — Odblokowany surowiec (ASCII)</t>
+          <t>Kopalnia — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>glina</t>
-        </is>
-      </c>
+          <t>ruda</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -2652,7 +2746,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie glinianka · placement/render MAPA</t>
+          <t>ulepszenie kopalnia · placement/render MAPA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2669,17 +2763,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>glinianka.bonus.praca</t>
+          <t>kopalnia.bonus.praca</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Glinianka — bonus praca</t>
+          <t>Kopalnia — bonus praca</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -2704,17 +2799,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>kamieniolom.koszt_praca</t>
+          <t>glinianka.koszt_praca</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Kamieniołom — Koszt budowy</t>
+          <t>Glinianka — Koszt budowy</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>22</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -2722,7 +2818,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie kamieniolom · placement/render MAPA</t>
+          <t>ulepszenie glinianka · placement/render MAPA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2739,17 +2835,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>kamieniolom.epoka</t>
+          <t>glinianka.epoka</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Kamieniołom — Epoka odblokowania</t>
+          <t>Glinianka — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -2757,7 +2854,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie kamieniolom · placement/render MAPA</t>
+          <t>ulepszenie glinianka · placement/render MAPA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2774,19 +2871,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>kamieniolom.surowiecOdblokowany</t>
+          <t>glinianka.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Kamieniołom — Odblokowany surowiec (ASCII)</t>
+          <t>Glinianka — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>kamien</t>
-        </is>
-      </c>
+          <t>glina</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -2794,7 +2892,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie kamieniolom · placement/render MAPA</t>
+          <t>ulepszenie glinianka · placement/render MAPA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2811,17 +2909,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>kamieniolom.bonus.praca</t>
+          <t>glinianka.bonus.praca</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Kamieniołom — bonus praca</t>
+          <t>Glinianka — bonus praca</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>pkt/turę</t>
@@ -2846,25 +2945,26 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>kamieniolom.bonus.kamien</t>
+          <t>kamieniolom.koszt_praca</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Kamieniołom — bonus kamien</t>
+          <t>Kamieniołom — Koszt budowy</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>tileYield / surowce</t>
+          <t>ulepszenie kamieniolom · placement/render MAPA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2881,25 +2981,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wyrab.koszt_praca</t>
+          <t>kamieniolom.epoka</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>Wyrąb — Koszt budowy</t>
+          <t>Kamieniołom — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Praca</t>
+          <t>1=Kamień…3=Żelazo</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie wyrab · placement/render MAPA</t>
+          <t>ulepszenie kamieniolom · placement/render MAPA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2916,25 +3017,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wyrab.epoka</t>
+          <t>kamieniolom.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>Wyrąb — Epoka odblokowania</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
-      </c>
+          <t>Kamieniołom — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>kamien</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1=Kamień…3=Żelazo</t>
+          <t>klucz lub puste</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie wyrab · placement/render MAPA</t>
+          <t>ulepszenie kamieniolom · placement/render MAPA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2951,22 +3055,26 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>wyrab.surowiecOdblokowany</t>
+          <t>kamieniolom.bonus.praca</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>Wyrąb — Odblokowany surowiec (ASCII)</t>
-        </is>
-      </c>
+          <t>Kamieniołom — bonus praca</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>klucz lub puste</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie wyrab · placement/render MAPA</t>
+          <t>tileYield / surowce</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2983,25 +3091,26 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>wyrab.wycinka.praca_per_tura</t>
+          <t>kamieniolom.bonus.kamien</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>Wyrąb — Praca na turę wycinki</t>
+          <t>Kamieniołom — bonus kamien</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Praca</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>wyrąb lasu — 3 tury potem teren bazowy</t>
+          <t>tileYield / surowce</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3018,25 +3127,26 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wyrab.wycinka.tury</t>
+          <t>wyrab.koszt_praca</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>Wyrąb — Liczba tur wycinki</t>
+          <t>Wyrąb — Koszt budowy</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>tury</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>wyrąb lasu — 3 tury potem teren bazowy</t>
+          <t>ulepszenie wyrab · placement/render MAPA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3053,25 +3163,26 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>tartak.koszt_praca</t>
+          <t>wyrab.epoka</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>Tartak — Koszt budowy</t>
+          <t>Wyrąb — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Praca</t>
+          <t>1=Kamień…3=Żelazo</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie tartak · placement/render MAPA</t>
+          <t>ulepszenie wyrab · placement/render MAPA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3088,25 +3199,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tartak.epoka</t>
+          <t>wyrab.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>Tartak — Epoka odblokowania</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
+          <t>Wyrąb — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1=Kamień…3=Żelazo</t>
+          <t>klucz lub puste</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie tartak · placement/render MAPA</t>
+          <t>ulepszenie wyrab · placement/render MAPA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3123,27 +3232,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tartak.surowiecOdblokowany</t>
+          <t>wyrab.wycinka.praca_per_tura</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>Tartak — Odblokowany surowiec (ASCII)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>drewno</t>
-        </is>
-      </c>
+          <t>Wyrąb — Praca na turę wycinki</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>20</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>klucz lub puste</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie tartak · placement/render MAPA</t>
+          <t>wyrąb lasu — 3 tury potem teren bazowy</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3160,25 +3268,26 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tartak.bonus.praca</t>
+          <t>wyrab.wycinka.tury</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Tartak — bonus praca</t>
+          <t>Wyrąb — Liczba tur wycinki</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>3</v>
       </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>tury</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>tileYield / surowce</t>
+          <t>wyrąb lasu — 3 tury potem teren bazowy</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3195,17 +3304,18 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>fort.koszt_praca</t>
+          <t>tartak.koszt_praca</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Koszt budowy</t>
+          <t>Tartak — Koszt budowy</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>25</v>
       </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3213,7 +3323,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie fort · placement/render MAPA</t>
+          <t>ulepszenie tartak · placement/render MAPA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3230,17 +3340,18 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>fort.epoka</t>
+          <t>tartak.epoka</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Epoka odblokowania</t>
+          <t>Tartak — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -3248,7 +3359,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie fort · placement/render MAPA</t>
+          <t>ulepszenie tartak · placement/render MAPA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3265,14 +3376,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>fort.surowiecOdblokowany</t>
+          <t>tartak.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Odblokowany surowiec (ASCII)</t>
-        </is>
-      </c>
+          <t>Tartak — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>drewno</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -3280,7 +3397,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie fort · placement/render MAPA</t>
+          <t>ulepszenie tartak · placement/render MAPA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3297,25 +3414,26 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fort.bonus_obrona_proc</t>
+          <t>tartak.bonus.praca</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Bonus obrony (obozowanie)</t>
+          <t>Tartak — bonus praca</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>100</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie fort · placement/render MAPA</t>
+          <t>tileYield / surowce</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3332,20 +3450,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>fort.bonus_wymaga_obozowania</t>
+          <t>fort.koszt_praca</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Bonus obrony tylko przy obozowaniu</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
-      </c>
+          <t>Fort — Koszt budowy</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>25</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>tak/nie</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3367,20 +3486,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fort.zasieg_terytorium</t>
+          <t>fort.epoka</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Rozszerzenie terytorium</t>
+          <t>Fort — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>1=Kamień…3=Żelazo</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3402,20 +3522,18 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>fort.zasieg_pol</t>
+          <t>fort.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Zasięg kontroli pola</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
+          <t>Fort — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>klucz lub puste</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3437,20 +3555,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>fort.zasieg_kontroli</t>
+          <t>fort.bonus_obrona_proc</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>Fort / umocnienia — Zasięg kontroli (fort)</t>
+          <t>Fort — Bonus obrony (obozowanie)</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3472,25 +3591,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>droga.koszt_praca</t>
+          <t>fort.bonus_wymaga_obozowania</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>Droga — Koszt budowy</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>15</v>
-      </c>
+          <t>Fort — Bonus obrony tylko przy obozowaniu</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Praca</t>
+          <t>tak/nie</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie droga · placement/render MAPA</t>
+          <t>ulepszenie fort · placement/render MAPA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3507,25 +3627,26 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>droga.epoka</t>
+          <t>fort.zasieg_terytorium</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>Droga — Epoka odblokowania</t>
+          <t>Fort — Rozszerzenie terytorium</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1=Kamień…3=Żelazo</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie droga · placement/render MAPA</t>
+          <t>ulepszenie fort · placement/render MAPA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3542,22 +3663,26 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>droga.surowiecOdblokowany</t>
+          <t>fort.zasieg_pol</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>Droga — Odblokowany surowiec (ASCII)</t>
-        </is>
-      </c>
+          <t>Fort — Zasięg kontroli pola</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>klucz lub puste</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie droga · placement/render MAPA</t>
+          <t>ulepszenie fort · placement/render MAPA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3574,25 +3699,26 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>droga.bonus.handel</t>
+          <t>fort.zasieg_kontroli</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>Droga — bonus handel</t>
+          <t>Fort — Zasięg kontroli (fort)</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>pkt/turę</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>tileYield / surowce</t>
+          <t>ulepszenie fort · placement/render MAPA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3609,17 +3735,18 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>posterunek.koszt_praca</t>
+          <t>droga.koszt_praca</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>Posterunek (Strażnica) — Koszt budowy</t>
+          <t>Droga — Koszt budowy</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>30</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
           <t>Praca</t>
@@ -3627,7 +3754,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie posterunek · placement/render MAPA</t>
+          <t>ulepszenie droga · placement/render MAPA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3644,17 +3771,18 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>posterunek.epoka</t>
+          <t>droga.epoka</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>Posterunek (Strażnica) — Epoka odblokowania</t>
+          <t>Droga — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
           <t>1=Kamień…3=Żelazo</t>
@@ -3662,7 +3790,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie posterunek · placement/render MAPA</t>
+          <t>ulepszenie droga · placement/render MAPA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3679,14 +3807,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>posterunek.surowiecOdblokowany</t>
+          <t>droga.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>Posterunek (Strażnica) — Odblokowany surowiec (ASCII)</t>
-        </is>
-      </c>
+          <t>Droga — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
           <t>klucz lub puste</t>
@@ -3694,7 +3823,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie posterunek · placement/render MAPA</t>
+          <t>ulepszenie droga · placement/render MAPA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3711,25 +3840,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>posterunek.bonus_obrona_proc</t>
+          <t>droga.bonus.handel</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>Posterunek (Strażnica) — Bonus obrony (obozowanie)</t>
+          <t>Droga — bonus handel</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>50</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie posterunek · placement/render MAPA</t>
+          <t>tileYield / surowce</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3746,25 +3876,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>posterunek.bonus_wymaga_obozowania</t>
+          <t>droga_brukowana.koszt_praca</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>Posterunek (Strażnica) — Bonus obrony tylko przy obozowaniu</t>
-        </is>
-      </c>
-      <c r="D40" t="b">
-        <v>1</v>
-      </c>
+          <t>Droga brukowana — Koszt budowy</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>25</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>tak/nie</t>
+          <t>Praca</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie posterunek · placement/render MAPA</t>
+          <t>ulepszenie droga_brukowana · placement/render MAPA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3781,25 +3912,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>posterunek.zasieg_terytorium</t>
+          <t>droga_brukowana.epoka</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>Posterunek (Strażnica) — Rozszerzenie terytorium</t>
+          <t>Droga brukowana — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>1=Kamień…3=Żelazo</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie posterunek · placement/render MAPA</t>
+          <t>ulepszenie droga_brukowana · placement/render MAPA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3816,28 +3948,421 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>droga_brukowana.surowiecOdblokowany</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Droga brukowana — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>klucz lub puste</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie droga_brukowana · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A-IMP-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>popalnia_brazu.koszt_praca</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Popalnia brązu — Koszt budowy</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>22</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Praca</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie popalnia_brazu · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A-IMP-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>popalnia_brazu.epoka</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Popalnia brązu — Epoka odblokowania</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1=Kamień…3=Żelazo</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie popalnia_brazu · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A-IMP-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>popalnia_brazu.surowiecOdblokowany</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Popalnia brązu — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ruda</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>klucz lub puste</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie popalnia_brazu · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A-IMP-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>popalnia_brazu.bonus.praca</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Popalnia brązu — bonus praca</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>tileYield / surowce</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>A-IMP-046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>posterunek.koszt_praca</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Posterunek (Strażnica) — Koszt budowy</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>30</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Praca</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie posterunek · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A-IMP-047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>posterunek.epoka</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Posterunek (Strażnica) — Epoka odblokowania</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1=Kamień…3=Żelazo</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie posterunek · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A-IMP-048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>posterunek.surowiecOdblokowany</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Posterunek (Strażnica) — Odblokowany surowiec (ASCII)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>klucz lub puste</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie posterunek · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A-IMP-049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>posterunek.bonus_obrona_proc</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Posterunek (Strażnica) — Bonus obrony (obozowanie)</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>50</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie posterunek · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A-IMP-050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>posterunek.bonus_wymaga_obozowania</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>Posterunek (Strażnica) — Bonus obrony tylko przy obozowaniu</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>tak/nie</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie posterunek · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A-IMP-051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>posterunek.zasieg_terytorium</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Posterunek (Strażnica) — Rozszerzenie terytorium</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>5</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>heksy</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>ulepszenie posterunek · placement/render MAPA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>terrain-improvements.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A-IMP-052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>posterunek.zasieg_pol</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>Posterunek (Strażnica) — Zasięg kontroli pola</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D53" t="n">
         <v>5</v>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
         <is>
           <t>heksy</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G53" s="3" t="inlineStr">
         <is>
           <t>ulepszenie posterunek · placement/render MAPA</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>terrain-improvements.json</t>
         </is>
@@ -3854,7 +4379,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3912,57 +4437,57 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-RUCH-LAK</t>
+          <t>A-PLON-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ruch.costs.Laka</t>
+          <t>plony.types.laka.zywnosc</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Łąka</t>
+          <t>Łąka — bazowy plon zywnosc</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-RUCH-ROW</t>
+          <t>A-PLON-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ruch.costs.Rownina</t>
+          <t>plony.types.laka.praca</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Równina</t>
+          <t>Łąka — bazowy plon praca</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -3970,239 +4495,239 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-RUCH-PUS</t>
+          <t>A-PLON-003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ruch.costs.Pustynia</t>
+          <t>plony.types.laka.handel</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Pustynia</t>
+          <t>Łąka — bazowy plon handel</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-RUCH-WYB</t>
+          <t>A-PLON-004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ruch.costs.Wybrzeze</t>
+          <t>plony.types.laka.drewno</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Wybrzeże</t>
+          <t>Łąka — bazowy plon drewno</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>99</v>
+        <v>1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-RUCH-WZG</t>
+          <t>A-PLON-005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ruch.costs.Wzgorza</t>
+          <t>plony.types.laka.kamien</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Wzgórza</t>
+          <t>Łąka — bazowy plon kamien</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-RUCH-GOR</t>
+          <t>A-PLON-006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ruch.costs.Gory</t>
+          <t>plony.types.rownina.zywnosc</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Góry</t>
+          <t>Równina — bazowy plon zywnosc</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-RUCH-MOR</t>
+          <t>A-PLON-007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ruch.costs.Morze</t>
+          <t>plony.types.rownina.praca</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Koszt ruchu jednostki — Morze</t>
+          <t>Równina — bazowy plon praca</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>99</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1–99 (99=nieprzechodnie)</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>units/setup.ts movementCost</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-RUCH-LAS</t>
+          <t>A-PLON-008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ruch.forestExtra</t>
+          <t>plony.types.rownina.handel</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Dopłata ruchu przez las (nakładka)</t>
+          <t>Równina — bazowy plon handel</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -4210,22 +4735,1502 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0–3</t>
+          <t>0–8 typowo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>punkty ruchu</t>
+          <t>pkt/turę</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>ruch po heksie z lasem</t>
+          <t>economy.ts tileYield · okolica miasta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>terrain-movement.json</t>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A-PLON-009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>plony.types.rownina.drewno</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Równina — bazowy plon drewno</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A-PLON-010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>plony.types.rownina.kamien</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Równina — bazowy plon kamien</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A-PLON-011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>plony.types.wzgorza.zywnosc</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Wzgórza — bazowy plon zywnosc</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A-PLON-012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>plony.types.wzgorza.praca</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Wzgórza — bazowy plon praca</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A-PLON-013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>plony.types.wzgorza.handel</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Wzgórza — bazowy plon handel</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A-PLON-014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>plony.types.wzgorza.drewno</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Wzgórza — bazowy plon drewno</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>A-PLON-015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>plony.types.wzgorza.kamien</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Wzgórza — bazowy plon kamien</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>A-PLON-016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>plony.types.gory.zywnosc</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Góry — bazowy plon zywnosc</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A-PLON-017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>plony.types.gory.praca</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Góry — bazowy plon praca</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>A-PLON-018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>plony.types.gory.handel</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Góry — bazowy plon handel</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>A-PLON-019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>plony.types.gory.drewno</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Góry — bazowy plon drewno</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>A-PLON-020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>plony.types.gory.kamien</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>Góry — bazowy plon kamien</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A-PLON-021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>plony.types.wybrzeze.zywnosc</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Wybrzeże — bazowy plon zywnosc</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>A-PLON-022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>plony.types.wybrzeze.praca</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Wybrzeże — bazowy plon praca</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>A-PLON-023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>plony.types.wybrzeze.handel</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Wybrzeże — bazowy plon handel</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>A-PLON-024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>plony.types.wybrzeze.drewno</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Wybrzeże — bazowy plon drewno</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A-PLON-025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>plony.types.wybrzeze.kamien</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Wybrzeże — bazowy plon kamien</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A-PLON-026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>plony.types.morze.zywnosc</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>Morze — bazowy plon zywnosc</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>2</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A-PLON-027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>plony.types.morze.praca</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Morze — bazowy plon praca</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>A-PLON-028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>plony.types.morze.handel</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>Morze — bazowy plon handel</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>A-PLON-029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>plony.types.morze.drewno</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Morze — bazowy plon drewno</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>A-PLON-030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>plony.types.morze.kamien</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Morze — bazowy plon kamien</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A-PLON-031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>plony.types.pustynia.zywnosc</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Pustynia — bazowy plon zywnosc</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>A-PLON-032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>plony.types.pustynia.praca</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Pustynia — bazowy plon praca</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>A-PLON-033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>plony.types.pustynia.handel</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Pustynia — bazowy plon handel</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>A-PLON-034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>plony.types.pustynia.drewno</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>Pustynia — bazowy plon drewno</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>A-PLON-035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>plony.types.pustynia.kamien</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Pustynia — bazowy plon kamien</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>0–8 typowo</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>economy.ts tileYield · okolica miasta</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>A-PLON-036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>plony.mod.rzeka.zywnosc</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Rzeka — zywnosc</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>A-PLON-037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>plony.mod.rzeka.praca</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Rzeka — praca</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>A-PLON-038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>plony.mod.rzeka.handel</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Rzeka — handel</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>A-PLON-039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>plony.mod.rzeka.drewno</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Rzeka — drewno</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>A-PLON-040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>plony.mod.rzeka.kamien</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Rzeka — kamien</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>A-PLON-041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>plony.mod.las.zywnosc</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Las (nakładka) — zywnosc</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A-PLON-042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>plony.mod.las.praca</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Las (nakładka) — praca</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>A-PLON-043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>plony.mod.las.handel</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Las (nakładka) — handel</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>A-PLON-044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>plony.mod.las.drewno</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Las (nakładka) — drewno</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>A-PLON-045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>plony.mod.las.kamien</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Modyfikator Las (nakładka) — kamien</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-3…+5</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>pkt/turę</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>bonus nakładki / rzeki na heks</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>terrain-yields.json</t>
         </is>
       </c>
     </row>
@@ -4298,290 +6303,320 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-FOG-SIGHT</t>
+          <t>A-RUCH-LAK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mgla.default_sight_jednostki</t>
+          <t>ruch.costs.Laka</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Domyślny promień wzroku jednostki (hexDistance)</t>
+          <t>Koszt ruchu jednostki — Łąka</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2–5 typowo</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>mgła — visibility.ts DEFAULT_SIGHT (wpięcie Integrator)</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-ZAS-MIASTO</t>
+          <t>A-RUCH-ROW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nota.miasto_zasieg_terytorium</t>
+          <t>ruch.costs.Rownina</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>NOTA: miasto bazowe zasięg terytorium (nie ulepszenie)</t>
+          <t>Koszt ruchu jednostki — Równina</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>stałe ref EKONOMIA</t>
+          <t>1–99 (99=nieprzechodnie)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>zakładanie kolejnego miasta — Panel-B / cities</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(tylko nota — bez eksportu)</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-ZAS-POST-ZAS</t>
+          <t>A-RUCH-PUS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>posterunek.zasieg_terytorium</t>
+          <t>ruch.costs.Pustynia</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Posterunek — zasieg terytorium</t>
+          <t>Koszt ruchu jednostki — Pustynia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>2</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1–99 (99=nieprzechodnie)</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-ZAS-POST-ZAS</t>
+          <t>A-RUCH-WYB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>posterunek.zasieg_pol</t>
+          <t>ruch.costs.Wybrzeze</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Posterunek — zasieg pol</t>
+          <t>Koszt ruchu jednostki — Wybrzeże</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>99</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1–99 (99=nieprzechodnie)</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-ZAS-POST-BON</t>
+          <t>A-RUCH-WZG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>posterunek.bonus_obrona_proc</t>
+          <t>ruch.costs.Wzgorza</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Posterunek — bonus obrona proc</t>
+          <t>Koszt ruchu jednostki — Wzgórza</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>50</v>
+        <v>2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1–99 (99=nieprzechodnie)</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-ZAS-FORT-ZAS</t>
+          <t>A-RUCH-GOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fort.zasieg_terytorium</t>
+          <t>ruch.costs.Gory</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Fort — zasieg terytorium</t>
+          <t>Koszt ruchu jednostki — Góry</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>99</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1–99 (99=nieprzechodnie)</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-ZAS-FORT-ZAS</t>
+          <t>A-RUCH-MOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fort.zasieg_pol</t>
+          <t>ruch.costs.Morze</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Fort — zasieg pol</t>
+          <t>Koszt ruchu jednostki — Morze</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>99</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1–99 (99=nieprzechodnie)</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>units/setup.ts movementCost</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-ZAS-FORT-BON</t>
+          <t>A-RUCH-LAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fort.bonus_obrona_proc</t>
+          <t>ruch.forestExtra</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Fort — bonus obrona proc</t>
+          <t>Dopłata ruchu przez las (nakładka)</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0–3</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>punkty ruchu</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>terytorium + mgła posterunku</t>
+          <t>ruch po heksie z lasem</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>terrain-improvements.json</t>
+          <t>terrain-movement.json</t>
         </is>
       </c>
     </row>
@@ -4596,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4654,25 +6689,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-GEN-DEF-W</t>
+          <t>A-FOG-SIGHT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>generator.default_width</t>
+          <t>mgla.default_sight_jednostki</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Domyślna szerokość siatki (dev / fallback generator.ts)</t>
+          <t>Domyślny promień wzroku jednostki (hexDistance)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20–200</t>
+          <t>2–5 typowo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -4682,37 +6717,37 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>generateMap() gdy brak rozmiaru z menu</t>
+          <t>mgła — visibility.ts DEFAULT_SIGHT (wpięcie Integrator)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>map-gen-params.json (wpięcie Integrator P3)</t>
+          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-GEN-DEF-H</t>
+          <t>A-ZAS-MIASTO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>generator.default_height</t>
+          <t>nota.miasto_zasieg_terytorium</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Domyślna wysokość siatki (dev / fallback)</t>
+          <t>NOTA: miasto bazowe zasięg terytorium (nie ulepszenie)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>15–150</t>
+          <t>stałe ref EKONOMIA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4722,34 +6757,35 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>generateMap() fallback</t>
+          <t>zakładanie kolejnego miasta — Panel-B / cities</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>(tylko nota — bez eksportu)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-W</t>
+          <t>A-ZAS-POST-ZAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.malenki.w</t>
+          <t>posterunek.zasieg_terytorium</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Malenki — szerokość</t>
+          <t>Posterunek — zasieg terytorium</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -4757,34 +6793,35 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-H</t>
+          <t>A-ZAS-POST-ZAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.malenki.h</t>
+          <t>posterunek.zasieg_pol</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Malenki — wysokość</t>
+          <t>Posterunek — zasieg pol</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>26</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -4792,69 +6829,71 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-W</t>
+          <t>A-ZAS-POST-BON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.maly.w</t>
+          <t>posterunek.bonus_obrona_proc</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Mały — szerokość</t>
+          <t>Posterunek — bonus obrona proc</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-GEN-MAL-H</t>
+          <t>A-ZAS-FORT-ZAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.maly.h</t>
+          <t>fort.zasieg_terytorium</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Mały — wysokość</t>
+          <t>Fort — zasieg terytorium</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>37</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -4862,34 +6901,35 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-GEN-STA-W</t>
+          <t>A-ZAS-FORT-ZAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.standardowy.w</t>
+          <t>fort.zasieg_pol</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Standardowy — szerokość</t>
+          <t>Fort — zasieg pol</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>84</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>heksy</t>
@@ -4897,187 +6937,48 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-GEN-STA-H</t>
+          <t>A-ZAS-FORT-BON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>generator.rozmiar_dims.standardowy.h</t>
+          <t>fort.bonus_obrona_proc</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Rozmiar mapy Standardowy — wysokość</t>
+          <t>Fort — bonus obrona proc</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>60</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>heksy</t>
+          <t>%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>menuLabelToDims · generujSwiat</t>
+          <t>terytorium + mgła posterunku</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A-GEN-DUZ-W</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>generator.rozmiar_dims.duzy.w</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Rozmiar mapy Duży — szerokość</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>120</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>heksy</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>menuLabelToDims · generujSwiat</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>A-GEN-DUZ-H</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>generator.rozmiar_dims.duzy.h</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Rozmiar mapy Duży — wysokość</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>84</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>heksy</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>menuLabelToDims · generujSwiat</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A-GEN-OGR-W</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>generator.rozmiar_dims.ogromny.w</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Rozmiar mapy Ogromny — szerokość</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>168</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>heksy</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>menuLabelToDims · generujSwiat</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>A-GEN-OGR-H</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>generator.rozmiar_dims.ogromny.h</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Rozmiar mapy Ogromny — wysokość</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>119</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>heksy</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>menuLabelToDims · generujSwiat</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
+          <t>terrain-improvements.json</t>
         </is>
       </c>
     </row>
@@ -5150,75 +7051,75 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A-ZLO-R-MIED</t>
+          <t>A-GEN-DEF-W</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>zloza.miedz.rarity</t>
+          <t>generator.default_width</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „miedz” (placeDeposits)</t>
+          <t>Domyślna szerokość siatki (dev / fallback generator.ts)</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>36</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0,02–0,25</t>
+          <t>20–200</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>generateMap() gdy brak rozmiaru z menu</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>map-gen-params.json</t>
+          <t>map-gen-params.json (wpięcie Integrator P3)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A-ZLO-R-ZELA</t>
+          <t>A-GEN-DEF-H</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>zloza.zelazo.rarity</t>
+          <t>generator.default_height</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „zelazo” (placeDeposits)</t>
+          <t>Domyślna wysokość siatki (dev / fallback)</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.08</v>
+        <v>28</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0,02–0,25</t>
+          <t>15–150</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>generateMap() fallback</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -5230,35 +7131,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A-ZLO-R-GLIN</t>
+          <t>A-GEN-MAL-W</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>zloza.glina.rarity</t>
+          <t>generator.rozmiar_dims.malenki.w</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „glina” (placeDeposits)</t>
+          <t>Rozmiar mapy Malenki — szerokość</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>76</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -5270,35 +7167,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A-ZLO-R-KONI</t>
+          <t>A-GEN-MAL-H</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>zloza.konie.rarity</t>
+          <t>generator.rozmiar_dims.malenki.h</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „konie” (placeDeposits)</t>
+          <t>Rozmiar mapy Malenki — wysokość</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5310,35 +7203,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A-ZLO-R-WEGI</t>
+          <t>A-GEN-MAL-W</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>zloza.wegiel.rarity</t>
+          <t>generator.rozmiar_dims.maly.w</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „wegiel” (placeDeposits)</t>
+          <t>Rozmiar mapy Mały — szerokość</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -5350,35 +7239,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A-ZLO-R-OWCE</t>
+          <t>A-GEN-MAL-H</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>zloza.owce.rarity</t>
+          <t>generator.rozmiar_dims.maly.h</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „owce” (placeDeposits)</t>
+          <t>Rozmiar mapy Mały — wysokość</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -5390,35 +7275,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A-ZLO-R-BYDL</t>
+          <t>A-GEN-STA-W</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>zloza.bydlo.rarity</t>
+          <t>generator.rozmiar_dims.standardowy.w</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „bydlo” (placeDeposits)</t>
+          <t>Rozmiar mapy Standardowy — szerokość</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -5430,35 +7311,31 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A-ZLO-R-LAMA</t>
+          <t>A-GEN-STA-H</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>zloza.lama.rarity</t>
+          <t>generator.rozmiar_dims.standardowy.h</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „lama” (placeDeposits)</t>
+          <t>Rozmiar mapy Standardowy — wysokość</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -5470,35 +7347,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A-ZLO-R-LUKS</t>
+          <t>A-GEN-DUZ-W</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>zloza.luksus.rarity</t>
+          <t>generator.rozmiar_dims.duzy.w</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „luksus” (placeDeposits)</t>
+          <t>Rozmiar mapy Duży — szerokość</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -5510,35 +7383,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-ZLO-R-SOL</t>
+          <t>A-GEN-DUZ-H</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>zloza.sol.rarity</t>
+          <t>generator.rozmiar_dims.duzy.h</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Rzadkość złoża „sol” (placeDeposits)</t>
+          <t>Rozmiar mapy Duży — wysokość</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0,02–0,25</t>
-        </is>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0–1 ułamek</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -5550,35 +7419,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-ZLO-E-MIED</t>
+          <t>A-GEN-OGR-W</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zloza.miedz.min_epoka</t>
+          <t>generator.rozmiar_dims.ogromny.w</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>Minimalna epoka widoczności złoża „miedz”</t>
+          <t>Rozmiar mapy Ogromny — szerokość</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1=Kamień…3=Żelazo</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>deposit-era.ts · mgła surowców</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5590,35 +7455,31 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A-ZLO-E-ZELA</t>
+          <t>A-GEN-OGR-H</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>zloza.zelazo.min_epoka</t>
+          <t>generator.rozmiar_dims.ogromny.h</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>Minimalna epoka widoczności złoża „zelazo”</t>
+          <t>Rozmiar mapy Ogromny — wysokość</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1–3</t>
-        </is>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1=Kamień…3=Żelazo</t>
+          <t>heksy</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>deposit-era.ts · mgła surowców</t>
+          <t>menuLabelToDims · generujSwiat</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5633,6 +7494,552 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Parametr</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Opis</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Wartość</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Zakres/dozwolone</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Jednostka</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Wpływ na grę</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Plik źródłowy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-MIED</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>zloza.miedz.rarity</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „miedz” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-ZELA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>zloza.zelazo.rarity</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „zelazo” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-GLIN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>zloza.glina.rarity</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „glina” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-KONI</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zloza.konie.rarity</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „konie” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-WEGI</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>zloza.wegiel.rarity</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „wegiel” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-OWCE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>zloza.owce.rarity</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „owce” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-BYDL</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>zloza.bydlo.rarity</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „bydlo” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-LAMA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>zloza.lama.rarity</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „lama” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-LUKS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>zloza.luksus.rarity</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „luksus” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A-ZLO-R-SOL</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>zloza.sol.rarity</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Rzadkość złoża „sol” (placeDeposits)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0,02–0,25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0–1 ułamek</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>generator — ile heksów dostaje złoże (teren w kodzie)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A-ZLO-E-MIED</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>zloza.miedz.min_epoka</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Minimalna epoka widoczności złoża „miedz”</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>1=Kamień…3=Żelazo</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>deposit-era.ts · mgła surowców</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A-ZLO-E-ZELA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>zloza.zelazo.min_epoka</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>Minimalna epoka widoczności złoża „zelazo”</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1–3</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1=Kamień…3=Żelazo</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>deposit-era.ts · mgła surowców</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>map-gen-params.json</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5870,7 +8277,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -5910,7 +8317,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -5950,7 +8357,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>120</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -6032,6 +8439,7 @@
       <c r="D10" t="n">
         <v>0.63</v>
       </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -6067,6 +8475,7 @@
       <c r="D11" t="n">
         <v>0.58</v>
       </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -6102,6 +8511,7 @@
       <c r="D12" t="n">
         <v>0.65</v>
       </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -6137,6 +8547,7 @@
       <c r="D13" t="n">
         <v>0.58</v>
       </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -6172,6 +8583,7 @@
       <c r="D14" t="n">
         <v>0.5</v>
       </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>0–1</t>
@@ -6345,392 +8757,6 @@
       <c r="H18" t="inlineStr">
         <is>
           <t>map-gen-params.json (kod P3)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Parametr</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Opis</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Wartość</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Zakres/dozwolone</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Jednostka</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>Wpływ na grę</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Plik źródłowy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-MAL</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.mala</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Mała</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-MAL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.mala</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Mała</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-SRE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.srednia</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Średnia</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-SRE</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.srednia</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Średnia</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-DUZ</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.duza</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Duża</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-DUZ</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.duza</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Duża</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A-MAP-TYP-OGR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>mapa_skala.aktywne_typy.ogromna</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Aktywne typy cywilizacji na mapie Ogromna</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>9</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3–9</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>typy</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>cluster spawn · E2-Q1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A-MAP-RYW-OGR</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>mapa_skala.domyslni_rywale.ogromna</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Domyślna liczba rywali AI — mapa Ogromna</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>8</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1–8</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>cyw</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>kreator nowej gry</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>map-gen-params.json</t>
         </is>
       </c>
     </row>

--- a/panele-sterowania/Panel-A.xlsx
+++ b/panele-sterowania/Panel-A.xlsx
@@ -3981,12 +3981,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>popalnia_brazu.koszt_praca</t>
+          <t>kopalnia_miedzi.koszt_praca</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>Popalnia brązu — Koszt budowy</t>
+          <t>Kopalnia miedzi — Koszt budowy</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie popalnia_brazu · placement/render MAPA</t>
+          <t>ulepszenie kopalnia_miedzi · placement/render MAPA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4017,12 +4017,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>popalnia_brazu.epoka</t>
+          <t>kopalnia_miedzi.epoka</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>Popalnia brązu — Epoka odblokowania</t>
+          <t>Kopalnia miedzi — Epoka odblokowania</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie popalnia_brazu · placement/render MAPA</t>
+          <t>ulepszenie kopalnia_miedzi · placement/render MAPA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>popalnia_brazu.surowiecOdblokowany</t>
+          <t>kopalnia_miedzi.surowiecOdblokowany</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>Popalnia brązu — Odblokowany surowiec (ASCII)</t>
+          <t>Kopalnia miedzi — Odblokowany surowiec (ASCII)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>ulepszenie popalnia_brazu · placement/render MAPA</t>
+          <t>ulepszenie kopalnia_miedzi · placement/render MAPA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>popalnia_brazu.bonus.praca</t>
+          <t>kopalnia_miedzi.bonus.praca</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Popalnia brązu — bonus praca</t>
+          <t>Kopalnia miedzi — bonus praca</t>
         </is>
       </c>
       <c r="D46" t="n">

--- a/panele-sterowania/Panel-A.xlsx
+++ b/panele-sterowania/Panel-A.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gen-panel-a.py · 2026-07-09</t>
+          <t>gen-panel-a.py · 2026-07-19</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
@@ -3277,7 +3277,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">

--- a/panele-sterowania/Panel-A.xlsx
+++ b/panele-sterowania/Panel-A.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ulepszenia-FOOD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ulepszenia-inne" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plony-terenow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ruch-po-terenie" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zasięgi-mgła" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-rozmiary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zloza-generator" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generator-E2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mapa-skala" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Eksporty" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="_INFO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Ulepszenia-FOOD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ulepszenia-inne" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Plony-terenow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ruch-po-terenie" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Zasięgi-mgła" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Generator-rozmiary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Zloza-generator" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Generator-E2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Mapa-skala" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="_Eksporty" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gen-panel-a.py · 2026-07-19</t>
+          <t>gen-panel-a.py · 2026-07-24</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -883,7 +883,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -7811,7 +7811,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
